--- a/backend/outputs/processed_Variant Attribute Analysis (1).xlsx
+++ b/backend/outputs/processed_Variant Attribute Analysis (1).xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -55,10 +58,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,556 +442,563 @@
   </sheetPr>
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Attribute</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Values</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Total_Annual_Revenue</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Percent_of_Total_Revenue</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Unique_Customers</t>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Total Annual Revenue</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Percentage of Total Revenue</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t># of Unique Customers</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Monetization Model</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Subscription</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="4" t="n">
         <v>973276</v>
       </c>
-      <c r="D2" t="n">
-        <v>57.6</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="D2" s="5" t="n">
+        <v>0.5760000000000001</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>34</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Monetization Model</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Perpetual</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="4" t="n">
         <v>716941</v>
       </c>
-      <c r="D3" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3" s="5" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Deployment Method</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>SW (Customer Managed)</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="4" t="n">
         <v>1577753</v>
       </c>
-      <c r="D4" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" s="5" t="n">
+        <v>0.9329999999999999</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>56</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Deployment Method</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>SaaS</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="4" t="n">
         <v>112464</v>
       </c>
-      <c r="D5" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" s="5" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Hyperscaler</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Any cloud env</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="4" t="n">
         <v>74105</v>
       </c>
-      <c r="D6" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" s="5" t="n">
+        <v>0.659</v>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Hyperscaler</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Synexa Cloud</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="4" t="n">
         <v>38359</v>
       </c>
-      <c r="D7" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" s="5" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Edition</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Basic</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="4" t="n">
         <v>1444998</v>
       </c>
-      <c r="D8" t="n">
-        <v>91.59999999999999</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" s="5" t="n">
+        <v>0.9159999999999999</v>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Edition</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Premium</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="4" t="n">
         <v>132755</v>
       </c>
-      <c r="D9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" s="5" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Support Type</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="4" t="n">
         <v>1335738</v>
       </c>
-      <c r="D10" t="n">
-        <v>79</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" s="5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>47</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Support Type</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Advanced Support</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="4" t="n">
         <v>256980</v>
       </c>
-      <c r="D11" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" s="5" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Support Type</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Extended Support</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="4" t="n">
         <v>97499</v>
       </c>
-      <c r="D12" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" s="5" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Environment Type</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Non- Production</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="4" t="n">
         <v>795727</v>
       </c>
-      <c r="D13" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" s="5" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Environment Type</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Production</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="4" t="n">
         <v>782026</v>
       </c>
-      <c r="D14" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" s="5" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Reserved</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="4" t="n">
         <v>1109900</v>
       </c>
-      <c r="D15" t="n">
-        <v>70.3</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" s="5" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Reserved</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="4" t="n">
         <v>467853</v>
       </c>
-      <c r="D16" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" s="5" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Add-On</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Orchestrator</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="4" t="n">
         <v>189257</v>
       </c>
-      <c r="D17" t="n">
-        <v>100</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>7</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Chargeable Unit</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Virtual Processor Core</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="4" t="n">
         <v>1444998</v>
       </c>
-      <c r="D18" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" s="5" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>51</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Chargeable Unit</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Resource Unit</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="4" t="n">
         <v>245219</v>
       </c>
-      <c r="D19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19" s="5" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Synexa X</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="4" t="n">
         <v>802687</v>
       </c>
-      <c r="D20" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="D20" s="5" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Synexa X</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="4" t="n">
         <v>775066</v>
       </c>
-      <c r="D21" t="n">
-        <v>49.1</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21" s="5" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Sales Motion</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="4" t="n">
         <v>1364188</v>
       </c>
-      <c r="D22" t="n">
-        <v>80.7</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="D22" s="5" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>48</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Sales Motion</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Renewal</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="4" t="n">
         <v>239452</v>
       </c>
-      <c r="D23" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="D23" s="5" t="n">
+        <v>0.142</v>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Sales Motion</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Upgrade</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" s="4" t="n">
         <v>86577</v>
       </c>
-      <c r="D24" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24" s="5" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>License Term</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Annual</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" s="4" t="n">
         <v>1419589</v>
       </c>
-      <c r="D25" t="n">
-        <v>84</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="D25" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>49</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>License Term</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="4" t="n">
         <v>270628</v>
       </c>
-      <c r="D26" t="n">
-        <v>16</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="D26" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>10</v>
       </c>
     </row>
